--- a/Base/Backlog_42.xlsx
+++ b/Base/Backlog_42.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adrianokj\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franciscoj\Python_Initial\Pyhton_Web\Base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A1B005D-66AF-4DD4-AB9F-234ED39DC3F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EDC85AF-F0D8-4D6E-8442-5E6A3D3D7A31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="273" xr2:uid="{89A3EF9E-2AF9-420D-85DF-9BB5B68F651F}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="273" xr2:uid="{89A3EF9E-2AF9-420D-85DF-9BB5B68F651F}"/>
   </bookViews>
   <sheets>
     <sheet name="ITI" sheetId="2" r:id="rId1"/>
@@ -121,7 +121,7 @@
     <t>Jose Ortiz</t>
   </si>
   <si>
-    <t>Erick Silva</t>
+    <t>Erick da Silva</t>
   </si>
 </sst>
 </file>
@@ -661,7 +661,7 @@
         <v>11</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C2" s="9">
         <v>2025</v>
@@ -676,7 +676,7 @@
         <v>45954</v>
       </c>
       <c r="G2" s="9">
-        <v>4261</v>
+        <v>4071</v>
       </c>
       <c r="H2" s="3">
         <v>45931</v>
@@ -711,7 +711,7 @@
         <v>45954</v>
       </c>
       <c r="G3" s="9">
-        <v>4071</v>
+        <v>4008</v>
       </c>
       <c r="H3" s="3">
         <v>45931</v>
@@ -746,7 +746,7 @@
         <v>45954</v>
       </c>
       <c r="G4" s="9">
-        <v>4008</v>
+        <v>3867</v>
       </c>
       <c r="H4" s="3">
         <v>45931</v>
@@ -766,7 +766,7 @@
         <v>11</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="C5" s="9">
         <v>2025</v>
@@ -781,7 +781,7 @@
         <v>45954</v>
       </c>
       <c r="G5" s="9">
-        <v>3974</v>
+        <v>3863</v>
       </c>
       <c r="H5" s="3">
         <v>45931</v>
@@ -801,7 +801,7 @@
         <v>11</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C6" s="9">
         <v>2025</v>
@@ -816,7 +816,7 @@
         <v>45954</v>
       </c>
       <c r="G6" s="9">
-        <v>3962</v>
+        <v>3516</v>
       </c>
       <c r="H6" s="3">
         <v>45931</v>
@@ -836,7 +836,7 @@
         <v>11</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="C7" s="9">
         <v>2025</v>
@@ -851,7 +851,7 @@
         <v>45954</v>
       </c>
       <c r="G7" s="9">
-        <v>3945</v>
+        <v>3425</v>
       </c>
       <c r="H7" s="3">
         <v>45931</v>
@@ -871,7 +871,7 @@
         <v>11</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C8" s="9">
         <v>2025</v>
@@ -886,7 +886,7 @@
         <v>45954</v>
       </c>
       <c r="G8" s="9">
-        <v>3939</v>
+        <v>3424</v>
       </c>
       <c r="H8" s="3">
         <v>45931</v>
@@ -921,7 +921,7 @@
         <v>45954</v>
       </c>
       <c r="G9" s="9">
-        <v>3867</v>
+        <v>3224</v>
       </c>
       <c r="H9" s="3">
         <v>45931</v>
@@ -956,7 +956,7 @@
         <v>45954</v>
       </c>
       <c r="G10" s="9">
-        <v>3863</v>
+        <v>3060</v>
       </c>
       <c r="H10" s="3">
         <v>45931</v>
@@ -976,7 +976,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C11" s="9">
         <v>2025</v>
@@ -991,10 +991,10 @@
         <v>45954</v>
       </c>
       <c r="G11" s="9">
-        <v>3844</v>
+        <v>1835</v>
       </c>
       <c r="H11" s="3">
-        <v>45931</v>
+        <v>45901</v>
       </c>
       <c r="I11" s="2">
         <v>45950</v>
@@ -1011,7 +1011,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="C12" s="9">
         <v>2025</v>
@@ -1026,7 +1026,7 @@
         <v>45954</v>
       </c>
       <c r="G12" s="9">
-        <v>3710</v>
+        <v>4261</v>
       </c>
       <c r="H12" s="3">
         <v>45931</v>
@@ -1046,7 +1046,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C13" s="9">
         <v>2025</v>
@@ -1061,7 +1061,7 @@
         <v>45954</v>
       </c>
       <c r="G13" s="9">
-        <v>3647</v>
+        <v>3264</v>
       </c>
       <c r="H13" s="3">
         <v>45931</v>
@@ -1096,7 +1096,7 @@
         <v>45954</v>
       </c>
       <c r="G14" s="9">
-        <v>3624</v>
+        <v>3710</v>
       </c>
       <c r="H14" s="3">
         <v>45931</v>
@@ -1116,7 +1116,7 @@
         <v>11</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="C15" s="9">
         <v>2025</v>
@@ -1131,7 +1131,7 @@
         <v>45954</v>
       </c>
       <c r="G15" s="9">
-        <v>3516</v>
+        <v>3624</v>
       </c>
       <c r="H15" s="3">
         <v>45931</v>
@@ -1151,7 +1151,7 @@
         <v>11</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="C16" s="9">
         <v>2025</v>
@@ -1166,7 +1166,7 @@
         <v>45954</v>
       </c>
       <c r="G16" s="9">
-        <v>3425</v>
+        <v>3384</v>
       </c>
       <c r="H16" s="3">
         <v>45931</v>
@@ -1186,7 +1186,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C17" s="9">
         <v>2025</v>
@@ -1201,7 +1201,7 @@
         <v>45954</v>
       </c>
       <c r="G17" s="9">
-        <v>3424</v>
+        <v>3962</v>
       </c>
       <c r="H17" s="3">
         <v>45931</v>
@@ -1236,7 +1236,7 @@
         <v>45954</v>
       </c>
       <c r="G18" s="9">
-        <v>3418</v>
+        <v>3939</v>
       </c>
       <c r="H18" s="3">
         <v>45931</v>
@@ -1256,7 +1256,7 @@
         <v>11</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C19" s="9">
         <v>2025</v>
@@ -1271,7 +1271,7 @@
         <v>45954</v>
       </c>
       <c r="G19" s="9">
-        <v>3404</v>
+        <v>3647</v>
       </c>
       <c r="H19" s="3">
         <v>45931</v>
@@ -1291,7 +1291,7 @@
         <v>11</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C20" s="9">
         <v>2025</v>
@@ -1306,7 +1306,7 @@
         <v>45954</v>
       </c>
       <c r="G20" s="9">
-        <v>3384</v>
+        <v>3418</v>
       </c>
       <c r="H20" s="3">
         <v>45931</v>
@@ -1361,7 +1361,7 @@
         <v>11</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="C22" s="9">
         <v>2025</v>
@@ -1376,7 +1376,7 @@
         <v>45954</v>
       </c>
       <c r="G22" s="9">
-        <v>3264</v>
+        <v>3945</v>
       </c>
       <c r="H22" s="3">
         <v>45931</v>
@@ -1396,7 +1396,7 @@
         <v>11</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="C23" s="9">
         <v>2025</v>
@@ -1411,7 +1411,7 @@
         <v>45954</v>
       </c>
       <c r="G23" s="9">
-        <v>3224</v>
+        <v>3188</v>
       </c>
       <c r="H23" s="3">
         <v>45931</v>
@@ -1431,7 +1431,7 @@
         <v>11</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C24" s="9">
         <v>2025</v>
@@ -1446,7 +1446,7 @@
         <v>45954</v>
       </c>
       <c r="G24" s="9">
-        <v>3188</v>
+        <v>3974</v>
       </c>
       <c r="H24" s="3">
         <v>45931</v>
@@ -1466,7 +1466,7 @@
         <v>11</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C25" s="9">
         <v>2025</v>
@@ -1481,7 +1481,7 @@
         <v>45954</v>
       </c>
       <c r="G25" s="9">
-        <v>3060</v>
+        <v>3844</v>
       </c>
       <c r="H25" s="3">
         <v>45931</v>
@@ -1501,7 +1501,7 @@
         <v>11</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C26" s="9">
         <v>2025</v>
@@ -1516,10 +1516,10 @@
         <v>45954</v>
       </c>
       <c r="G26" s="9">
-        <v>1835</v>
+        <v>3404</v>
       </c>
       <c r="H26" s="3">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="I26" s="2">
         <v>45950</v>
@@ -1596,7 +1596,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:K26" xr:uid="{69362A46-9E44-40AB-81A2-018EE27C1DC6}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K26">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K27">
       <sortCondition ref="B1:B26"/>
     </sortState>
   </autoFilter>

--- a/Base/Backlog_42.xlsx
+++ b/Base/Backlog_42.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franciscoj\Python_Initial\Pyhton_Web\Base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EDC85AF-F0D8-4D6E-8442-5E6A3D3D7A31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B39D131-1FE4-4DC4-9A61-C085BDD04EB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="273" xr2:uid="{89A3EF9E-2AF9-420D-85DF-9BB5B68F651F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="273" activeTab="1" xr2:uid="{89A3EF9E-2AF9-420D-85DF-9BB5B68F651F}"/>
   </bookViews>
   <sheets>
     <sheet name="ITI" sheetId="2" r:id="rId1"/>
@@ -100,9 +100,6 @@
     <t>SPN</t>
   </si>
   <si>
-    <t>Denis Silva</t>
-  </si>
-  <si>
     <t>Willian Rios</t>
   </si>
   <si>
@@ -122,6 +119,9 @@
   </si>
   <si>
     <t>Erick da Silva</t>
+  </si>
+  <si>
+    <t>Denis da Silva</t>
   </si>
 </sst>
 </file>
@@ -1081,7 +1081,7 @@
         <v>11</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C14" s="9">
         <v>2025</v>
@@ -1116,7 +1116,7 @@
         <v>11</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C15" s="9">
         <v>2025</v>
@@ -1151,7 +1151,7 @@
         <v>11</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C16" s="9">
         <v>2025</v>
@@ -1361,7 +1361,7 @@
         <v>11</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C22" s="9">
         <v>2025</v>
@@ -1396,7 +1396,7 @@
         <v>11</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C23" s="9">
         <v>2025</v>
@@ -1431,7 +1431,7 @@
         <v>11</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C24" s="9">
         <v>2025</v>
@@ -1664,7 +1664,7 @@
         <v>18</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C2" s="1">
         <v>2025</v>
@@ -1691,7 +1691,7 @@
         <v>13</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -1699,7 +1699,7 @@
         <v>18</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C3" s="1">
         <v>2025</v>
@@ -1726,7 +1726,7 @@
         <v>13</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -1734,7 +1734,7 @@
         <v>18</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C4" s="1">
         <v>2025</v>
@@ -1761,7 +1761,7 @@
         <v>13</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
@@ -1769,7 +1769,7 @@
         <v>18</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C5" s="1">
         <v>2025</v>
@@ -1796,7 +1796,7 @@
         <v>13</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
@@ -1804,7 +1804,7 @@
         <v>18</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C6" s="1">
         <v>2025</v>
@@ -1831,7 +1831,7 @@
         <v>13</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
@@ -1839,7 +1839,7 @@
         <v>18</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C7" s="1">
         <v>2025</v>
@@ -1866,7 +1866,7 @@
         <v>13</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
@@ -1874,7 +1874,7 @@
         <v>18</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C8" s="1">
         <v>2025</v>
@@ -1901,7 +1901,7 @@
         <v>13</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
@@ -1909,7 +1909,7 @@
         <v>18</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C9" s="1">
         <v>2025</v>
@@ -1936,7 +1936,7 @@
         <v>13</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
@@ -1944,7 +1944,7 @@
         <v>18</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C10" s="1">
         <v>2025</v>
@@ -1971,7 +1971,7 @@
         <v>13</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
